--- a/hasil_cleaning.xlsx
+++ b/hasil_cleaning.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,11 +439,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>url_gambar</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>waktu_scraping</t>
         </is>
       </c>
@@ -455,301 +446,271 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Postingan di Grid Instagram Bisa Diubah Posisinya, Begini Caranya</t>
+          <t>Format dan Jadwal MSC Mobile Legends di Esports World Cup (EWC) 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Postingan di Grid Instagram Bisa Diubah Posisinya, Begini Caranya</t>
+          <t>Format dan Jadwal MSC Mobile Legends di Esports World Cup EWC 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/mobile-apps/d-8525701/postingan-di-grid-instagram-bisa-diubah-posisinya-begini-caranya</t>
+          <t>https://inet.detik.com/esport/d-8526212/format-dan-jadwal-msc-mobile-legends-di-esports-world-cup-ewc-2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/mobile-apps/d-8525701/postingan-di-grid-instagram-bisa-diubah-posisinya-begini-caranya</t>
+          <t>httpsinetdetikcomesportdformatdanjadwalmscmobilelegendsdiesportsworldcupewc</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/09/27/ilustrasi-instagram_43.jpeg?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jadwal Playoff MPL ID S17 Hari Ini: Bigetron Vs Evos</t>
+          <t>Apple Kenalkan Framework AI Baru dan Xcode 27 di WWDC 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jadwal Playoff MPL ID S17 Hari Ini: Bigetron Vs Evos</t>
+          <t>Apple Kenalkan Framework AI Baru dan Xcode 27 di WWDC 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/esport/d-8525693/jadwal-playoff-mpl-id-s17-hari-ini-bigetron-vs-evos</t>
+          <t>https://inet.detik.com/cyberlife/d-8526130/apple-kenalkan-framework-ai-baru-dan-xcode-27-di-wwdc-2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/esport/d-8525693/jadwal-playoff-mpl-id-s17-hari-ini-bigetron-vs-evos</t>
+          <t>httpsinetdetikcomcyberlifedapplekenalkanframeworkaibarudanxcodediwwdc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/10/jadwal-mpl-id-s17-week-3-hari-ini-navi-vs-evos-1775789438104_43.jpeg?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Video: Agenda WWDC 2026 Terakhir Tim Cook Jadi CEO Apple</t>
+          <t>Komentar Ibunda Elon Musk Soal Anaknya yang Orang Baru Tahu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Video: Agenda WWDC 2026 Terakhir Tim Cook Jadi CEO Apple</t>
+          <t>Komentar Ibunda Elon Musk Soal Anaknya yang Orang Baru Tahu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/detiktv/d-8525718/video-agenda-wwdc-2026-terakhir-tim-cook-jadi-ceo-apple</t>
+          <t>https://inet.detik.com/cyberlife/d-8526025/komentar-ibunda-elon-musk-soal-anaknya-yang-orang-baru-tahu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/detiktv/d-8525718/video-agenda-wwdc-2026-terakhir-tim-cook-jadi-ceo-apple</t>
+          <t>httpsinetdetikcomcyberlifedkomentaribundaelonmusksoalanaknyayangorangbarutahu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/25/tim-cook-1777096396523_43.jpeg?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trionda, Bola Piala Dunia 2026 Canggih untuk Bantu Wasit</t>
+          <t>Yandex Berdayakan Operator Telekomunikasi untuk Bangun Produk Sendiri</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trionda, Bola Piala Dunia 2026 Canggih untuk Bantu Wasit</t>
+          <t>Yandex Berdayakan Operator Telekomunikasi untuk Bangun Produk Sendiri</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8525616/trionda-bola-piala-dunia-2026-canggih-untuk-bantu-wasit</t>
+          <t>https://inet.detik.com/telecommunication/d-8525916/yandex-berdayakan-operator-telekomunikasi-untuk-bangun-produk-sendiri</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8525616/trionda-bola-piala-dunia-2026-canggih-untuk-bantu-wasit</t>
+          <t>httpsinetdetikcomtelecommunicationdyandexberdayakanoperatortelekomunikasiuntukbangunproduksendiri</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/03/trionda-1759476752270_43.jpeg?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Apple Rombak Maps, Music, Podcasts &amp; iCloud di iOS 27, Ini Fitur Barunya</t>
+          <t>Pantas Gen Z Keranjingan Video Sinematik, Ini Alasannya</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apple Rombak Maps, Music, Podcasts &amp; iCloud di iOS 27, Ini Fitur Barunya</t>
+          <t>Pantas Gen Z Keranjingan Video Sinematik Ini Alasannya</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/consumer/d-8525613/apple-rombak-maps-music-podcasts-icloud-di-ios-27-ini-fitur-barunya</t>
+          <t>https://inet.detik.com/consumer/d-8525884/pantas-gen-z-keranjingan-video-sinematik-ini-alasannya</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/consumer/d-8525613/apple-rombak-maps-music-podcasts-icloud-di-ios-27-ini-fitur-barunya</t>
+          <t>httpsinetdetikcomconsumerdpantasgenzkeranjinganvideosinematikinialasannya</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/ios-27-1781057796800_43.jpeg?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Video: NASA Gandeng Astronot Italia-AS untuk Misi Artemis III</t>
+          <t>Postingan di Grid Instagram Bisa Diubah Posisinya, Begini Caranya</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Video: NASA Gandeng Astronot Italia-AS untuk Misi Artemis III</t>
+          <t>Postingan di Grid Instagram Bisa Diubah Posisinya Begini Caranya</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/detiktv/d-8525612/video-nasa-gandeng-astronot-italia-as-untuk-misi-artemis-iii</t>
+          <t>https://inet.detik.com/mobile-apps/d-8525701/postingan-di-grid-instagram-bisa-diubah-posisinya-begini-caranya</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/detiktv/d-8525612/video-nasa-gandeng-astronot-italia-as-untuk-misi-artemis-iii</t>
+          <t>httpsinetdetikcommobileappsdpostingandigridinstagrambisadiubahposisinyabeginicaranya</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/space-artemisastronauts-1781057681797_43.jpeg?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nah Loh! Selingkuhan Bill Gates Ternyata yang Kenalkan ke Epstein</t>
+          <t>Jadwal Playoff MPL ID S17 Hari Ini: Bigetron Vs Evos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nah Loh! Selingkuhan Bill Gates Ternyata yang Kenalkan ke Epstein</t>
+          <t>Jadwal Playoff MPL ID S17 Hari Ini Bigetron Vs Evos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8525139/nah-loh-selingkuhan-bill-gates-ternyata-yang-kenalkan-ke-epstein</t>
+          <t>https://inet.detik.com/esport/d-8525693/jadwal-playoff-mpl-id-s17-hari-ini-bigetron-vs-evos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8525139/nah-loh-selingkuhan-bill-gates-ternyata-yang-kenalkan-ke-epstein</t>
+          <t>httpsinetdetikcomesportdjadwalplayoffmplidshariinibigetronvsevos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/05/bill-gates-1770250296944_43.jpeg?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14 Foto Foto Kelam Perang Dunia II, Bukti Nyata Kengerian yang Tak Terlupakan</t>
+          <t>Video: Agenda WWDC 2026 Terakhir Tim Cook Jadi CEO Apple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14 Foto Foto Kelam Perang Dunia II, Bukti Nyata Kengerian yang Tak Terlupakan</t>
+          <t>Video Agenda WWDC 2026 Terakhir Tim Cook Jadi CEO Apple</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/fotoinet/d-8525552/foto-kelam-perang-dunia-ii-bukti-nyata-kengerian-yang-tak-terlupakan</t>
+          <t>https://inet.detik.com/detiktv/d-8525718/video-agenda-wwdc-2026-terakhir-tim-cook-jadi-ceo-apple</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/fotoinet/d-8525552/foto-kelam-perang-dunia-ii-bukti-nyata-kengerian-yang-tak-terlupakan</t>
+          <t>httpsinetdetikcomdetiktvdvideoagendawwdcterakhirtimcookjadiceoapple</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/foto-kelam-perang-1781055113755_43.webp?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WhatsApp Cabut Dukungan untuk iOS Lawas Ini, Segera Update iPhone Kalian!</t>
+          <t>Trionda, Bola Piala Dunia 2026 Canggih untuk Bantu Wasit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WhatsApp Cabut Dukungan untuk iOS Lawas Ini, Segera Update iPhone Kalian!</t>
+          <t>Trionda Bola Piala Dunia 2026 Canggih untuk Bantu Wasit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/mobile-apps/d-8525537/whatsapp-cabut-dukungan-untuk-ios-lawas-ini-segera-update-iphone-kalian</t>
+          <t>https://inet.detik.com/cyberlife/d-8525616/trionda-bola-piala-dunia-2026-canggih-untuk-bantu-wasit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/mobile-apps/d-8525537/whatsapp-cabut-dukungan-untuk-ios-lawas-ini-segera-update-iphone-kalian</t>
+          <t>httpsinetdetikcomcyberlifedtriondabolapialaduniacanggihuntukbantuwasit</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/18/ilustrasi-whatsapp-1771389858556_43.jpeg?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Drama Siri AI di Eropa: Apple Salahkan DMA, UE Membalas</t>
+          <t>Apple Rombak Maps, Music, Podcasts &amp; iCloud di iOS 27, Ini Fitur Barunya</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Drama Siri AI di Eropa: Apple Salahkan DMA, UE Membalas</t>
+          <t>Apple Rombak Maps Music Podcasts iCloud di iOS 27 Ini Fitur Barunya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/consumer/d-8525512/drama-siri-ai-di-eropa-apple-salahkan-dma-ue-membalas</t>
+          <t>https://inet.detik.com/consumer/d-8525613/apple-rombak-maps-music-podcasts-icloud-di-ios-27-ini-fitur-barunya</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/consumer/d-8525512/drama-siri-ai-di-eropa-apple-salahkan-dma-ue-membalas</t>
+          <t>httpsinetdetikcomconsumerdapplerombakmapsmusicpodcastsiclouddiiosinifiturbarunya</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/siri-ai-1781052453392_43.png?w=250&amp;q=90</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>46183.59498403651</v>
+          <t>10062026</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/hasil_cleaning.xlsx
+++ b/hasil_cleaning.xlsx
@@ -446,270 +446,270 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Format dan Jadwal MSC Mobile Legends di Esports World Cup (EWC) 2026</t>
+          <t>Misteri Anjing Hantu Amazon Terkuak Setelah 25 Tahun Penelitian</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Format dan Jadwal MSC Mobile Legends di Esports World Cup EWC 2026</t>
+          <t>Misteri Anjing Hantu Amazon Terkuak Setelah 25 Tahun Penelitian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/esport/d-8526212/format-dan-jadwal-msc-mobile-legends-di-esports-world-cup-ewc-2026</t>
+          <t>https://inet.detik.com/science/d-8534054/misteri-anjing-hantu-amazon-terkuak-setelah-25-tahun-penelitian</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomesportdformatdanjadwalmscmobilelegendsdiesportsworldcupewc</t>
+          <t>httpsinetdetikcomsciencedmisterianjinghantuamazonterkuaksetelahtahunpenelitian</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Apple Kenalkan Framework AI Baru dan Xcode 27 di WWDC 2026</t>
+          <t>Proyek Bendungan Raksasa China Bisa Jadi Malapetaka Buat India</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple Kenalkan Framework AI Baru dan Xcode 27 di WWDC 2026</t>
+          <t>Proyek Bendungan Raksasa China Bisa Jadi Malapetaka Buat India</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8526130/apple-kenalkan-framework-ai-baru-dan-xcode-27-di-wwdc-2026</t>
+          <t>https://inet.detik.com/science/d-8534000/proyek-bendungan-raksasa-china-bisa-jadi-malapetaka-buat-india</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomcyberlifedapplekenalkanframeworkaibarudanxcodediwwdc</t>
+          <t>httpsinetdetikcomsciencedproyekbendunganraksasachinabisajadimalapetakabuatindia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Komentar Ibunda Elon Musk Soal Anaknya yang Orang Baru Tahu</t>
+          <t>Heboh Penemuan Kuburan Jutaan Paus di Dasar Samudra Hindia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Komentar Ibunda Elon Musk Soal Anaknya yang Orang Baru Tahu</t>
+          <t>Heboh Penemuan Kuburan Jutaan Paus di Dasar Samudra Hindia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8526025/komentar-ibunda-elon-musk-soal-anaknya-yang-orang-baru-tahu</t>
+          <t>https://inet.detik.com/science/d-8533938/heboh-penemuan-kuburan-jutaan-paus-di-dasar-samudra-hindia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomcyberlifedkomentaribundaelonmusksoalanaknyayangorangbarutahu</t>
+          <t>httpsinetdetikcomsciencedhebohpenemuankuburanjutaanpausdidasarsamudrahindia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yandex Berdayakan Operator Telekomunikasi untuk Bangun Produk Sendiri</t>
+          <t>CRM Indonesia Rating Tertinggi, Barantum Raih 4,9/5 dari 1.200+ Ulasan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yandex Berdayakan Operator Telekomunikasi untuk Bangun Produk Sendiri</t>
+          <t>CRM Indonesia Rating Tertinggi Barantum Raih 495 dari 1200 Ulasan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/telecommunication/d-8525916/yandex-berdayakan-operator-telekomunikasi-untuk-bangun-produk-sendiri</t>
+          <t>https://inet.detik.com/business/d-8533936/crm-indonesia-rating-tertinggi-barantum-raih-4-9-5-dari-1-200-ulasan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomtelecommunicationdyandexberdayakanoperatortelekomunikasiuntukbangunproduksendiri</t>
+          <t>httpsinetdetikcombusinessdcrmindonesiaratingtertinggibarantumraihdariulasan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantas Gen Z Keranjingan Video Sinematik, Ini Alasannya</t>
+          <t>VCGamers Rilis Fitur Cuan, Bisa Dapat Penghasilan Tambahan!</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pantas Gen Z Keranjingan Video Sinematik Ini Alasannya</t>
+          <t>VCGamers Rilis Fitur Cuan Bisa Dapat Penghasilan Tambahan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/consumer/d-8525884/pantas-gen-z-keranjingan-video-sinematik-ini-alasannya</t>
+          <t>https://inet.detik.com/games-news/d-8533926/vcgamers-rilis-fitur-cuan-bisa-dapat-penghasilan-tambahan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomconsumerdpantasgenzkeranjinganvideosinematikinialasannya</t>
+          <t>httpsinetdetikcomgamesnewsdvcgamersrilisfiturcuanbisadapatpenghasilantambahan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Postingan di Grid Instagram Bisa Diubah Posisinya, Begini Caranya</t>
+          <t>Curhat Karyawan Meta yang Dipindah ke Divisi AI: Seperti Gulag</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Postingan di Grid Instagram Bisa Diubah Posisinya Begini Caranya</t>
+          <t>Curhat Karyawan Meta yang Dipindah ke Divisi AI Seperti Gulag</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/mobile-apps/d-8525701/postingan-di-grid-instagram-bisa-diubah-posisinya-begini-caranya</t>
+          <t>https://inet.detik.com/cyberlife/d-8533844/curhat-karyawan-meta-yang-dipindah-ke-divisi-ai-seperti-gulag</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>httpsinetdetikcommobileappsdpostingandigridinstagrambisadiubahposisinyabeginicaranya</t>
+          <t>httpsinetdetikcomcyberlifedcurhatkaryawanmetayangdipindahkedivisiaisepertigulag</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jadwal Playoff MPL ID S17 Hari Ini: Bigetron Vs Evos</t>
+          <t>Waktu Terbaik Borong Game PC! Valve Kasih Diskon Hingga 90% di Steam</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jadwal Playoff MPL ID S17 Hari Ini Bigetron Vs Evos</t>
+          <t>Waktu Terbaik Borong Game PC Valve Kasih Diskon Hingga 90 di Steam</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/esport/d-8525693/jadwal-playoff-mpl-id-s17-hari-ini-bigetron-vs-evos</t>
+          <t>https://inet.detik.com/games-news/d-8533784/waktu-terbaik-borong-game-pc-valve-kasih-diskon-hingga-90-di-steam</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomesportdjadwalplayoffmplidshariinibigetronvsevos</t>
+          <t>httpsinetdetikcomgamesnewsdwaktuterbaikboronggamepcvalvekasihdiskonhinggadisteam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Video: Agenda WWDC 2026 Terakhir Tim Cook Jadi CEO Apple</t>
+          <t>Tahan Raksasa Spanyol, Follower Vozinha Meroket 10.000%</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Video Agenda WWDC 2026 Terakhir Tim Cook Jadi CEO Apple</t>
+          <t>Tahan Raksasa Spanyol Follower Vozinha Meroket 10000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/detiktv/d-8525718/video-agenda-wwdc-2026-terakhir-tim-cook-jadi-ceo-apple</t>
+          <t>https://inet.detik.com/cyberlife/d-8533776/tahan-raksasa-spanyol-follower-vozinha-meroket-10-000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomdetiktvdvideoagendawwdcterakhirtimcookjadiceoapple</t>
+          <t>httpsinetdetikcomcyberlifedtahanraksasaspanyolfollowervozinhameroket</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Trionda, Bola Piala Dunia 2026 Canggih untuk Bantu Wasit</t>
+          <t>Ujian Terberat Industri AI Segera Dimulai</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trionda Bola Piala Dunia 2026 Canggih untuk Bantu Wasit</t>
+          <t>Ujian Terberat Industri AI Segera Dimulai</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8525616/trionda-bola-piala-dunia-2026-canggih-untuk-bantu-wasit</t>
+          <t>https://inet.detik.com/business/d-8533746/ujian-terberat-industri-ai-segera-dimulai</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomcyberlifedtriondabolapialaduniacanggihuntukbantuwasit</t>
+          <t>httpsinetdetikcombusinessdujianterberatindustriaisegeradimulai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Apple Rombak Maps, Music, Podcasts &amp; iCloud di iOS 27, Ini Fitur Barunya</t>
+          <t>10 Foto Cape Verde Tahan Spanyol, Kipernya Bikin Netizen Takjub</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apple Rombak Maps Music Podcasts iCloud di iOS 27 Ini Fitur Barunya</t>
+          <t>10 Foto Cape Verde Tahan Spanyol Kipernya Bikin Netizen Takjub</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/consumer/d-8525613/apple-rombak-maps-music-podcasts-icloud-di-ios-27-ini-fitur-barunya</t>
+          <t>https://inet.detik.com/fotoinet/d-8533716/cape-verde-tahan-spanyol-kipernya-bikin-netizen-takjub</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomconsumerdapplerombakmapsmusicpodcastsiclouddiiosinifiturbarunya</t>
+          <t>httpsinetdetikcomfotoinetdcapeverdetahanspanyolkipernyabikinnetizentakjub</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10062026</t>
+          <t>16062026</t>
         </is>
       </c>
     </row>

--- a/hasil_cleaning.xlsx
+++ b/hasil_cleaning.xlsx
@@ -446,270 +446,270 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Misteri Anjing Hantu Amazon Terkuak Setelah 25 Tahun Penelitian</t>
+          <t>Video: Xiaomi 17T Pro Udah Bisa Quickshare ke iPhone Tanpa Aplikasi Tambahan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Misteri Anjing Hantu Amazon Terkuak Setelah 25 Tahun Penelitian</t>
+          <t>Video Xiaomi 17T Pro Udah Bisa Quickshare ke iPhone Tanpa Aplikasi Tambahan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/science/d-8534054/misteri-anjing-hantu-amazon-terkuak-setelah-25-tahun-penelitian</t>
+          <t>https://inet.detik.com/detiktv/d-8535163/video-xiaomi-17t-pro-udah-bisa-quickshare-ke-iphone-tanpa-aplikasi-tambahan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomsciencedmisterianjinghantuamazonterkuaksetelahtahunpenelitian</t>
+          <t>httpsinetdetikcomdetiktvdvideoxiaomitproudahbisaquicksharekeiphonetanpaaplikasitambahan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Proyek Bendungan Raksasa China Bisa Jadi Malapetaka Buat India</t>
+          <t>Logitech G304 X Superlight &amp; G316 X 98 Hadir di RI, Gaming Makin Ngebut</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Proyek Bendungan Raksasa China Bisa Jadi Malapetaka Buat India</t>
+          <t>Logitech G304 X Superlight G316 X 98 Hadir di RI Gaming Makin Ngebut</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/science/d-8534000/proyek-bendungan-raksasa-china-bisa-jadi-malapetaka-buat-india</t>
+          <t>https://inet.detik.com/consumer/d-8534901/logitech-g304-x-superlight-g316-x-98-hadir-di-ri-gaming-makin-ngebut</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomsciencedproyekbendunganraksasachinabisajadimalapetakabuatindia</t>
+          <t>httpsinetdetikcomconsumerdlogitechgxsuperlightgxhadirdirigamingmakinngebut</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Heboh Penemuan Kuburan Jutaan Paus di Dasar Samudra Hindia</t>
+          <t>10 Foto Lionel Messi Hattrick, Dipuji Setinggi Langit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Heboh Penemuan Kuburan Jutaan Paus di Dasar Samudra Hindia</t>
+          <t>10 Foto Lionel Messi Hattrick Dipuji Setinggi Langit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/science/d-8533938/heboh-penemuan-kuburan-jutaan-paus-di-dasar-samudra-hindia</t>
+          <t>https://inet.detik.com/fotoinet/d-8535031/lionel-messi-hattrick-dipuji-setinggi-langit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomsciencedhebohpenemuankuburanjutaanpausdidasarsamudrahindia</t>
+          <t>httpsinetdetikcomfotoinetdlionelmessihattrickdipujisetinggilangit</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRM Indonesia Rating Tertinggi, Barantum Raih 4,9/5 dari 1.200+ Ulasan</t>
+          <t>Kampus Ini Sudah Lahirkan 12 Unicorn AI dan Hardware, Ada DJI di Baliknya</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CRM Indonesia Rating Tertinggi Barantum Raih 495 dari 1200 Ulasan</t>
+          <t>Kampus Ini Sudah Lahirkan 12 Unicorn AI dan Hardware Ada DJI di Baliknya</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/business/d-8533936/crm-indonesia-rating-tertinggi-barantum-raih-4-9-5-dari-1-200-ulasan</t>
+          <t>https://inet.detik.com/cyberlife/d-8534903/kampus-ini-sudah-lahirkan-12-unicorn-ai-dan-hardware-ada-dji-di-baliknya</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>httpsinetdetikcombusinessdcrmindonesiaratingtertinggibarantumraihdariulasan</t>
+          <t>httpsinetdetikcomcyberlifedkampusinisudahlahirkanunicornaidanhardwareadadjidibaliknya</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VCGamers Rilis Fitur Cuan, Bisa Dapat Penghasilan Tambahan!</t>
+          <t>Zuckerberg Bayar Rp 248 T untuk Bocah Ajaib, Hasilnya Belum Ada</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VCGamers Rilis Fitur Cuan Bisa Dapat Penghasilan Tambahan</t>
+          <t>Zuckerberg Bayar Rp 248 T untuk Bocah Ajaib Hasilnya Belum Ada</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/games-news/d-8533926/vcgamers-rilis-fitur-cuan-bisa-dapat-penghasilan-tambahan</t>
+          <t>https://inet.detik.com/business/d-8534912/zuckerberg-bayar-rp-248-t-untuk-bocah-ajaib-hasilnya-belum-ada</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomgamesnewsdvcgamersrilisfiturcuanbisadapatpenghasilantambahan</t>
+          <t>httpsinetdetikcombusinessdzuckerbergbayarrptuntukbocahajaibhasilnyabelumada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Curhat Karyawan Meta yang Dipindah ke Divisi AI: Seperti Gulag</t>
+          <t>WhatsApp di iPhone Kini Bisa Pakai 2 Nomor Sekaligus, Begini Caranya</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Curhat Karyawan Meta yang Dipindah ke Divisi AI Seperti Gulag</t>
+          <t>WhatsApp di iPhone Kini Bisa Pakai 2 Nomor Sekaligus Begini Caranya</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8533844/curhat-karyawan-meta-yang-dipindah-ke-divisi-ai-seperti-gulag</t>
+          <t>https://inet.detik.com/consumer/d-8534891/whatsapp-di-iphone-kini-bisa-pakai-2-nomor-sekaligus-begini-caranya</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomcyberlifedcurhatkaryawanmetayangdipindahkedivisiaisepertigulag</t>
+          <t>httpsinetdetikcomconsumerdwhatsappdiiphonekinibisapakainomorsekaligusbeginicaranya</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Waktu Terbaik Borong Game PC! Valve Kasih Diskon Hingga 90% di Steam</t>
+          <t>Tak Sabar Tunggu GTA 6, Pria Ini Bikin Tiruannya Pakai AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Waktu Terbaik Borong Game PC Valve Kasih Diskon Hingga 90 di Steam</t>
+          <t>Tak Sabar Tunggu GTA 6 Pria Ini Bikin Tiruannya Pakai AI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/games-news/d-8533784/waktu-terbaik-borong-game-pc-valve-kasih-diskon-hingga-90-di-steam</t>
+          <t>https://inet.detik.com/games-news/d-8534872/tak-sabar-tunggu-gta-6-pria-ini-bikin-tiruannya-pakai-ai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomgamesnewsdwaktuterbaikboronggamepcvalvekasihdiskonhinggadisteam</t>
+          <t>httpsinetdetikcomgamesnewsdtaksabartunggugtapriainibikintiruannyapakaiai</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tahan Raksasa Spanyol, Follower Vozinha Meroket 10.000%</t>
+          <t>15 Foto Hanya Mata Jeli yang Bisa Menemukan Sosok di Foto 'Penampakan' Ini</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tahan Raksasa Spanyol Follower Vozinha Meroket 10000</t>
+          <t>15 Foto Hanya Mata Jeli yang Bisa Menemukan Sosok di Foto Penampakan Ini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/cyberlife/d-8533776/tahan-raksasa-spanyol-follower-vozinha-meroket-10-000</t>
+          <t>https://inet.detik.com/fotoinet/d-8534856/hanya-mata-jeli-yang-bisa-menemukan-sosok-di-foto-penampakan-ini</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomcyberlifedtahanraksasaspanyolfollowervozinhameroket</t>
+          <t>httpsinetdetikcomfotoinetdhanyamatajeliyangbisamenemukansosokdifotopenampakanini</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ujian Terberat Industri AI Segera Dimulai</t>
+          <t>Haaland Menggila di Debut Piala Dunia 2026, Borong 2 Gol Bikin Heboh Medsos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ujian Terberat Industri AI Segera Dimulai</t>
+          <t>Haaland Menggila di Debut Piala Dunia 2026 Borong 2 Gol Bikin Heboh Medsos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/business/d-8533746/ujian-terberat-industri-ai-segera-dimulai</t>
+          <t>https://inet.detik.com/cyberlife/d-8534834/haaland-menggila-di-debut-piala-dunia-2026-borong-2-gol-bikin-heboh-medsos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>httpsinetdetikcombusinessdujianterberatindustriaisegeradimulai</t>
+          <t>httpsinetdetikcomcyberlifedhaalandmenggiladidebutpialaduniaboronggolbikinhebohmedsos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10 Foto Cape Verde Tahan Spanyol, Kipernya Bikin Netizen Takjub</t>
+          <t>Gibran Ingatkan Bahaya AI, Singgung Teknologi Tanpa Etika Itu Berbahaya</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10 Foto Cape Verde Tahan Spanyol Kipernya Bikin Netizen Takjub</t>
+          <t>Gibran Ingatkan Bahaya AI Singgung Teknologi Tanpa Etika Itu Berbahaya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://inet.detik.com/fotoinet/d-8533716/cape-verde-tahan-spanyol-kipernya-bikin-netizen-takjub</t>
+          <t>https://inet.detik.com/law-and-policy/d-8534804/gibran-ingatkan-bahaya-ai-singgung-teknologi-tanpa-etika-itu-berbahaya</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>httpsinetdetikcomfotoinetdcapeverdetahanspanyolkipernyabikinnetizentakjub</t>
+          <t>httpsinetdetikcomlawandpolicydgibraningatkanbahayaaisinggungteknologitanpaetikaituberbahaya</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16062026</t>
+          <t>17062026</t>
         </is>
       </c>
     </row>
